--- a/output/graficos_nacionales/plot_nacional_dispersion_o_ocup_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_dispersion_o_ocup_a_2024.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$D$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$D$347</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
   <si>
     <t xml:space="preserve">Comuna</t>
   </si>
@@ -546,6 +546,9 @@
     <t xml:space="preserve">Cabildo</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Vicente</t>
   </si>
   <si>
@@ -690,6 +693,9 @@
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
@@ -1068,7 +1074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:45</t>
+    <t xml:space="preserve">2026-09-18 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -3896,13 +3902,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>33.31</v>
+        <v>33.37</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>50933</v>
+        <v>10017</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>753659</v>
+        <v>736174</v>
       </c>
     </row>
     <row r="175">
@@ -3910,13 +3916,13 @@
         <v>177</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>33.27</v>
+        <v>33.31</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>52405</v>
+        <v>50933</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>797977</v>
+        <v>753659</v>
       </c>
     </row>
     <row r="176">
@@ -3924,13 +3930,13 @@
         <v>178</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>33.22</v>
+        <v>33.27</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>39609</v>
+        <v>52405</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>928420</v>
+        <v>797977</v>
       </c>
     </row>
     <row r="177">
@@ -3938,13 +3944,13 @@
         <v>179</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>33.17</v>
+        <v>33.22</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>100227</v>
+        <v>39609</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>756734.5</v>
+        <v>928420</v>
       </c>
     </row>
     <row r="178">
@@ -3952,13 +3958,13 @@
         <v>180</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>33.15</v>
+        <v>33.17</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>6305</v>
+        <v>100227</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>915140</v>
+        <v>756734.5</v>
       </c>
     </row>
     <row r="179">
@@ -3966,13 +3972,13 @@
         <v>181</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>32.89</v>
+        <v>33.15</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>57332</v>
+        <v>6305</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>767100</v>
+        <v>915140</v>
       </c>
     </row>
     <row r="180">
@@ -3980,13 +3986,13 @@
         <v>182</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>32.83</v>
+        <v>32.89</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>252826</v>
+        <v>57332</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>917500</v>
+        <v>767100</v>
       </c>
     </row>
     <row r="181">
@@ -3994,13 +4000,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>32.81</v>
+        <v>32.83</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>3048</v>
+        <v>252826</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>852400</v>
+        <v>917500</v>
       </c>
     </row>
     <row r="182">
@@ -4008,13 +4014,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>32.79</v>
+        <v>32.81</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>85998</v>
+        <v>3048</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>758210</v>
+        <v>852400</v>
       </c>
     </row>
     <row r="183">
@@ -4022,13 +4028,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>32.72</v>
+        <v>32.79</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>25611</v>
+        <v>85998</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>719037.5</v>
+        <v>758210</v>
       </c>
     </row>
     <row r="184">
@@ -4036,13 +4042,13 @@
         <v>186</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>32.65</v>
+        <v>32.72</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>38007</v>
+        <v>25611</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>857835</v>
+        <v>719037.5</v>
       </c>
     </row>
     <row r="185">
@@ -4050,13 +4056,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>32.64</v>
+        <v>32.65</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>47900</v>
+        <v>38007</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>862500</v>
+        <v>857835</v>
       </c>
     </row>
     <row r="186">
@@ -4064,13 +4070,13 @@
         <v>188</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>32.63</v>
+        <v>32.64</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>144642</v>
+        <v>47900</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>786347</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="187">
@@ -4081,10 +4087,10 @@
         <v>32.63</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>45358</v>
+        <v>144642</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>753888</v>
+        <v>786347</v>
       </c>
     </row>
     <row r="188">
@@ -4092,13 +4098,13 @@
         <v>190</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>32.61</v>
+        <v>32.63</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>8524</v>
+        <v>45358</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>950812</v>
+        <v>753888</v>
       </c>
     </row>
     <row r="189">
@@ -4106,13 +4112,13 @@
         <v>191</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>32.59</v>
+        <v>32.61</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>21981</v>
+        <v>8524</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>686945</v>
+        <v>950812</v>
       </c>
     </row>
     <row r="190">
@@ -4120,13 +4126,13 @@
         <v>192</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>32.55</v>
+        <v>32.59</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>12893</v>
+        <v>21981</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>726862</v>
+        <v>686945</v>
       </c>
     </row>
     <row r="191">
@@ -4134,13 +4140,13 @@
         <v>193</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>32.53</v>
+        <v>32.55</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>103953</v>
+        <v>12893</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>804938</v>
+        <v>726862</v>
       </c>
     </row>
     <row r="192">
@@ -4148,13 +4154,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>32.5</v>
+        <v>32.53</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>60509</v>
+        <v>103953</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>822543.5</v>
+        <v>804938</v>
       </c>
     </row>
     <row r="193">
@@ -4162,13 +4168,13 @@
         <v>195</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>32.45</v>
+        <v>32.5</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>53254</v>
+        <v>60509</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>708691</v>
+        <v>822543.5</v>
       </c>
     </row>
     <row r="194">
@@ -4176,13 +4182,13 @@
         <v>196</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>32.43</v>
+        <v>32.45</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>11329</v>
+        <v>53254</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>833844</v>
+        <v>708691</v>
       </c>
     </row>
     <row r="195">
@@ -4190,13 +4196,13 @@
         <v>197</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>32.41</v>
+        <v>32.43</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>15164</v>
+        <v>11329</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>730665</v>
+        <v>833844</v>
       </c>
     </row>
     <row r="196">
@@ -4204,13 +4210,13 @@
         <v>198</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>32.32</v>
+        <v>32.41</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>26151</v>
+        <v>15164</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>764925</v>
+        <v>730665</v>
       </c>
     </row>
     <row r="197">
@@ -4218,13 +4224,13 @@
         <v>199</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>42730</v>
+        <v>26151</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>792540</v>
+        <v>764925</v>
       </c>
     </row>
     <row r="198">
@@ -4232,13 +4238,13 @@
         <v>200</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>32.28</v>
+        <v>32.31</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>16641</v>
+        <v>42730</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>824806.5</v>
+        <v>792540</v>
       </c>
     </row>
     <row r="199">
@@ -4246,13 +4252,13 @@
         <v>201</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>32.24</v>
+        <v>32.28</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>18282</v>
+        <v>16641</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>808969.5</v>
+        <v>824806.5</v>
       </c>
     </row>
     <row r="200">
@@ -4263,10 +4269,10 @@
         <v>32.24</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>84683</v>
+        <v>18282</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>706930</v>
+        <v>808969.5</v>
       </c>
     </row>
     <row r="201">
@@ -4274,13 +4280,13 @@
         <v>203</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>32.08</v>
+        <v>32.24</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>16180</v>
+        <v>84683</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>736600</v>
+        <v>706930</v>
       </c>
     </row>
     <row r="202">
@@ -4291,10 +4297,10 @@
         <v>32.08</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>32780</v>
+        <v>16180</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>769128</v>
+        <v>736600</v>
       </c>
     </row>
     <row r="203">
@@ -4302,13 +4308,13 @@
         <v>205</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>32.06</v>
+        <v>32.08</v>
       </c>
       <c r="C203" s="2" t="n">
-        <v>13258</v>
+        <v>32780</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>743000</v>
+        <v>769128</v>
       </c>
     </row>
     <row r="204">
@@ -4316,13 +4322,13 @@
         <v>206</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>32.05</v>
+        <v>32.06</v>
       </c>
       <c r="C204" s="2" t="n">
-        <v>25290</v>
+        <v>13258</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>740889</v>
+        <v>743000</v>
       </c>
     </row>
     <row r="205">
@@ -4330,13 +4336,13 @@
         <v>207</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>31.96</v>
+        <v>32.05</v>
       </c>
       <c r="C205" s="2" t="n">
-        <v>18784</v>
+        <v>25290</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>697917</v>
+        <v>740889</v>
       </c>
     </row>
     <row r="206">
@@ -4344,13 +4350,13 @@
         <v>208</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>31.94</v>
+        <v>31.96</v>
       </c>
       <c r="C206" s="2" t="n">
-        <v>10937</v>
+        <v>18784</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>765960</v>
+        <v>697917</v>
       </c>
     </row>
     <row r="207">
@@ -4358,13 +4364,13 @@
         <v>209</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>31.84</v>
+        <v>31.94</v>
       </c>
       <c r="C207" s="2" t="n">
-        <v>15652</v>
+        <v>10937</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>741695</v>
+        <v>765960</v>
       </c>
     </row>
     <row r="208">
@@ -4372,13 +4378,13 @@
         <v>210</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>31.79</v>
+        <v>31.84</v>
       </c>
       <c r="C208" s="2" t="n">
-        <v>16459</v>
+        <v>15652</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>738395.5</v>
+        <v>741695</v>
       </c>
     </row>
     <row r="209">
@@ -4386,13 +4392,13 @@
         <v>211</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="C209" s="2" t="n">
-        <v>38781</v>
+        <v>16459</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>906409.5</v>
+        <v>738395.5</v>
       </c>
     </row>
     <row r="210">
@@ -4400,13 +4406,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>31.73</v>
+        <v>31.75</v>
       </c>
       <c r="C210" s="2" t="n">
-        <v>20190</v>
+        <v>38781</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>806988</v>
+        <v>906409.5</v>
       </c>
     </row>
     <row r="211">
@@ -4417,10 +4423,10 @@
         <v>31.73</v>
       </c>
       <c r="C211" s="2" t="n">
-        <v>28335</v>
+        <v>20190</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>729450</v>
+        <v>806988</v>
       </c>
     </row>
     <row r="212">
@@ -4428,13 +4434,13 @@
         <v>214</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="C212" s="2" t="n">
-        <v>4192</v>
+        <v>28335</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>836005</v>
+        <v>729450</v>
       </c>
     </row>
     <row r="213">
@@ -4442,13 +4448,13 @@
         <v>215</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>31.61</v>
+        <v>31.68</v>
       </c>
       <c r="C213" s="2" t="n">
-        <v>17846</v>
+        <v>4192</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>816865</v>
+        <v>836005</v>
       </c>
     </row>
     <row r="214">
@@ -4456,13 +4462,13 @@
         <v>216</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>31.6</v>
+        <v>31.61</v>
       </c>
       <c r="C214" s="2" t="n">
-        <v>23415</v>
+        <v>17846</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>762187.5</v>
+        <v>816865</v>
       </c>
     </row>
     <row r="215">
@@ -4470,13 +4476,13 @@
         <v>217</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>31.57</v>
+        <v>31.6</v>
       </c>
       <c r="C215" s="2" t="n">
-        <v>50566</v>
+        <v>23415</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>729219</v>
+        <v>762187.5</v>
       </c>
     </row>
     <row r="216">
@@ -4484,13 +4490,13 @@
         <v>218</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>31.48</v>
+        <v>31.57</v>
       </c>
       <c r="C216" s="2" t="n">
-        <v>3976</v>
+        <v>50566</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>875450</v>
+        <v>729219</v>
       </c>
     </row>
     <row r="217">
@@ -4498,13 +4504,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="C217" s="2" t="n">
-        <v>17644</v>
+        <v>3976</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>797748</v>
+        <v>875450</v>
       </c>
     </row>
     <row r="218">
@@ -4512,13 +4518,13 @@
         <v>220</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="C218" s="2" t="n">
-        <v>16232</v>
+        <v>17644</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>828459</v>
+        <v>797748</v>
       </c>
     </row>
     <row r="219">
@@ -4526,13 +4532,13 @@
         <v>221</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>31.42</v>
+        <v>31.44</v>
       </c>
       <c r="C219" s="2" t="n">
-        <v>23311</v>
+        <v>16232</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>1043083.5</v>
+        <v>828459</v>
       </c>
     </row>
     <row r="220">
@@ -4540,13 +4546,13 @@
         <v>222</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>31.39</v>
+        <v>31.42</v>
       </c>
       <c r="C220" s="2" t="n">
-        <v>15224</v>
+        <v>23311</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>703513.5</v>
+        <v>1043083.5</v>
       </c>
     </row>
     <row r="221">
@@ -4554,13 +4560,13 @@
         <v>223</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>31.38</v>
+        <v>31.39</v>
       </c>
       <c r="C221" s="2" t="n">
-        <v>4183</v>
+        <v>15224</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>867422.5</v>
+        <v>703513.5</v>
       </c>
     </row>
     <row r="222">
@@ -4568,13 +4574,13 @@
         <v>224</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>31.36</v>
+        <v>31.38</v>
       </c>
       <c r="C222" s="2" t="n">
-        <v>33419</v>
+        <v>4183</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>791677.5</v>
+        <v>867422.5</v>
       </c>
     </row>
     <row r="223">
@@ -4582,13 +4588,13 @@
         <v>225</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>31.29</v>
+        <v>31.38</v>
       </c>
       <c r="C223" s="2" t="n">
-        <v>20102</v>
+        <v>5563</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>750000</v>
+        <v>700568</v>
       </c>
     </row>
     <row r="224">
@@ -4596,13 +4602,13 @@
         <v>226</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>31.1</v>
+        <v>31.36</v>
       </c>
       <c r="C224" s="2" t="n">
-        <v>10559</v>
+        <v>33419</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>789380</v>
+        <v>791677.5</v>
       </c>
     </row>
     <row r="225">
@@ -4610,13 +4616,13 @@
         <v>227</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>30.86</v>
+        <v>31.29</v>
       </c>
       <c r="C225" s="2" t="n">
-        <v>16375</v>
+        <v>20102</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>633395</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="226">
@@ -4624,13 +4630,13 @@
         <v>228</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>30.78</v>
+        <v>31.1</v>
       </c>
       <c r="C226" s="2" t="n">
-        <v>17207</v>
+        <v>10559</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>693000</v>
+        <v>789380</v>
       </c>
     </row>
     <row r="227">
@@ -4638,13 +4644,13 @@
         <v>229</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>30.61</v>
+        <v>30.86</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>19076</v>
+        <v>16375</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>779467.5</v>
+        <v>633395</v>
       </c>
     </row>
     <row r="228">
@@ -4652,13 +4658,13 @@
         <v>230</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>30.53</v>
+        <v>30.78</v>
       </c>
       <c r="C228" s="2" t="n">
-        <v>8539</v>
+        <v>17207</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>770838</v>
+        <v>693000</v>
       </c>
     </row>
     <row r="229">
@@ -4666,13 +4672,13 @@
         <v>231</v>
       </c>
       <c r="B229" s="2" t="n">
-        <v>30.5</v>
+        <v>30.61</v>
       </c>
       <c r="C229" s="2" t="n">
-        <v>34225</v>
+        <v>19076</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>718785</v>
+        <v>779467.5</v>
       </c>
     </row>
     <row r="230">
@@ -4680,13 +4686,13 @@
         <v>232</v>
       </c>
       <c r="B230" s="2" t="n">
-        <v>30.49</v>
+        <v>30.53</v>
       </c>
       <c r="C230" s="2" t="n">
-        <v>37915</v>
+        <v>8539</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>717864</v>
+        <v>770838</v>
       </c>
     </row>
     <row r="231">
@@ -4694,13 +4700,13 @@
         <v>233</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>30.48</v>
+        <v>30.5</v>
       </c>
       <c r="C231" s="2" t="n">
-        <v>12083</v>
+        <v>34225</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>962083</v>
+        <v>718785</v>
       </c>
     </row>
     <row r="232">
@@ -4708,13 +4714,13 @@
         <v>234</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>30.46</v>
+        <v>30.49</v>
       </c>
       <c r="C232" s="2" t="n">
-        <v>38274</v>
+        <v>37915</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>668024</v>
+        <v>717864</v>
       </c>
     </row>
     <row r="233">
@@ -4722,13 +4728,13 @@
         <v>235</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>30.46</v>
+        <v>30.48</v>
       </c>
       <c r="C233" s="2" t="n">
-        <v>25667</v>
+        <v>12083</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>720000</v>
+        <v>962083</v>
       </c>
     </row>
     <row r="234">
@@ -4736,13 +4742,13 @@
         <v>236</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>30.37</v>
+        <v>30.46</v>
       </c>
       <c r="C234" s="2" t="n">
-        <v>4279</v>
+        <v>38274</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>964104</v>
+        <v>668024</v>
       </c>
     </row>
     <row r="235">
@@ -4750,13 +4756,13 @@
         <v>237</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>30.24</v>
+        <v>30.46</v>
       </c>
       <c r="C235" s="2" t="n">
-        <v>21316</v>
+        <v>25667</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>748264</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="236">
@@ -4764,13 +4770,13 @@
         <v>238</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>30.18</v>
+        <v>30.37</v>
       </c>
       <c r="C236" s="2" t="n">
-        <v>12731</v>
+        <v>4279</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>697291.5</v>
+        <v>964104</v>
       </c>
     </row>
     <row r="237">
@@ -4778,13 +4784,13 @@
         <v>239</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>30.18</v>
+        <v>30.24</v>
       </c>
       <c r="C237" s="2" t="n">
-        <v>7096</v>
+        <v>21316</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>981497</v>
+        <v>748264</v>
       </c>
     </row>
     <row r="238">
@@ -4792,13 +4798,13 @@
         <v>240</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>30.16</v>
+        <v>30.18</v>
       </c>
       <c r="C238" s="2" t="n">
-        <v>8301</v>
+        <v>12731</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>747300</v>
+        <v>697291.5</v>
       </c>
     </row>
     <row r="239">
@@ -4806,13 +4812,13 @@
         <v>241</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>30.06</v>
+        <v>30.18</v>
       </c>
       <c r="C239" s="2" t="n">
-        <v>42070</v>
+        <v>7096</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>732483</v>
+        <v>981497</v>
       </c>
     </row>
     <row r="240">
@@ -4820,13 +4826,13 @@
         <v>242</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>30.05</v>
+        <v>30.16</v>
       </c>
       <c r="C240" s="2" t="n">
-        <v>8716</v>
+        <v>8301</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>848750</v>
+        <v>747300</v>
       </c>
     </row>
     <row r="241">
@@ -4834,13 +4840,13 @@
         <v>243</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>29.99</v>
+        <v>30.06</v>
       </c>
       <c r="C241" s="2" t="n">
-        <v>37816</v>
+        <v>42070</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>843294</v>
+        <v>732483</v>
       </c>
     </row>
     <row r="242">
@@ -4848,13 +4854,13 @@
         <v>244</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>29.98</v>
+        <v>30.05</v>
       </c>
       <c r="C242" s="2" t="n">
-        <v>8966</v>
+        <v>8716</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>698241</v>
+        <v>848750</v>
       </c>
     </row>
     <row r="243">
@@ -4862,13 +4868,13 @@
         <v>245</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>29.91</v>
+        <v>29.99</v>
       </c>
       <c r="C243" s="2" t="n">
-        <v>881</v>
+        <v>37816</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>850000</v>
+        <v>843294</v>
       </c>
     </row>
     <row r="244">
@@ -4876,13 +4882,13 @@
         <v>246</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>29.89</v>
+        <v>29.98</v>
       </c>
       <c r="C244" s="2" t="n">
-        <v>8069</v>
+        <v>8966</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>684535</v>
+        <v>698241</v>
       </c>
     </row>
     <row r="245">
@@ -4890,13 +4896,13 @@
         <v>247</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>29.72</v>
+        <v>29.91</v>
       </c>
       <c r="C245" s="2" t="n">
-        <v>23440</v>
+        <v>881</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>758230</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="246">
@@ -4904,13 +4910,13 @@
         <v>248</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>29.58</v>
+        <v>29.89</v>
       </c>
       <c r="C246" s="2" t="n">
-        <v>30387</v>
+        <v>8069</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>675000</v>
+        <v>684535</v>
       </c>
     </row>
     <row r="247">
@@ -4918,13 +4924,13 @@
         <v>249</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>29.53</v>
+        <v>29.72</v>
       </c>
       <c r="C247" s="2" t="n">
-        <v>14321</v>
+        <v>23440</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>931830</v>
+        <v>758230</v>
       </c>
     </row>
     <row r="248">
@@ -4932,13 +4938,13 @@
         <v>250</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>29.41</v>
+        <v>29.58</v>
       </c>
       <c r="C248" s="2" t="n">
-        <v>30003</v>
+        <v>30387</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>741480</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="249">
@@ -4946,13 +4952,13 @@
         <v>251</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>29.28</v>
+        <v>29.53</v>
       </c>
       <c r="C249" s="2" t="n">
-        <v>2497</v>
+        <v>14321</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>904968</v>
+        <v>931830</v>
       </c>
     </row>
     <row r="250">
@@ -4960,13 +4966,13 @@
         <v>252</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>29.21</v>
+        <v>29.41</v>
       </c>
       <c r="C250" s="2" t="n">
-        <v>4986</v>
+        <v>30003</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>733740</v>
+        <v>741480</v>
       </c>
     </row>
     <row r="251">
@@ -4974,13 +4980,13 @@
         <v>253</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>29.21</v>
+        <v>29.28</v>
       </c>
       <c r="C251" s="2" t="n">
-        <v>9269</v>
+        <v>2497</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>875000</v>
+        <v>904968</v>
       </c>
     </row>
     <row r="252">
@@ -4988,13 +4994,13 @@
         <v>254</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>29.18</v>
+        <v>29.21</v>
       </c>
       <c r="C252" s="2" t="n">
-        <v>26787</v>
+        <v>4986</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>787500</v>
+        <v>733740</v>
       </c>
     </row>
     <row r="253">
@@ -5002,13 +5008,13 @@
         <v>255</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>29.08</v>
+        <v>29.21</v>
       </c>
       <c r="C253" s="2" t="n">
-        <v>13351</v>
+        <v>9269</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>750472</v>
+        <v>875000</v>
       </c>
     </row>
     <row r="254">
@@ -5016,13 +5022,13 @@
         <v>256</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>29.08</v>
+        <v>29.18</v>
       </c>
       <c r="C254" s="2" t="n">
-        <v>50410</v>
+        <v>26787</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>699994</v>
+        <v>787500</v>
       </c>
     </row>
     <row r="255">
@@ -5030,13 +5036,13 @@
         <v>257</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>29.07</v>
+        <v>29.08</v>
       </c>
       <c r="C255" s="2" t="n">
-        <v>58952</v>
+        <v>13351</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>735282</v>
+        <v>750472</v>
       </c>
     </row>
     <row r="256">
@@ -5044,13 +5050,13 @@
         <v>258</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>28.98</v>
+        <v>29.08</v>
       </c>
       <c r="C256" s="2" t="n">
-        <v>547</v>
+        <v>50410</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>920000</v>
+        <v>699994</v>
       </c>
     </row>
     <row r="257">
@@ -5058,13 +5064,13 @@
         <v>259</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>28.94</v>
+        <v>29.07</v>
       </c>
       <c r="C257" s="2" t="n">
-        <v>39260</v>
+        <v>58952</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>735750</v>
+        <v>735282</v>
       </c>
     </row>
     <row r="258">
@@ -5072,13 +5078,13 @@
         <v>260</v>
       </c>
       <c r="B258" s="2" t="n">
-        <v>28.81</v>
+        <v>28.98</v>
       </c>
       <c r="C258" s="2" t="n">
-        <v>21719</v>
+        <v>547</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>727604</v>
+        <v>920000</v>
       </c>
     </row>
     <row r="259">
@@ -5086,13 +5092,13 @@
         <v>261</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>28.76</v>
+        <v>28.94</v>
       </c>
       <c r="C259" s="2" t="n">
-        <v>6855</v>
+        <v>39260</v>
       </c>
       <c r="D259" s="2" t="n">
-        <v>724150</v>
+        <v>735750</v>
       </c>
     </row>
     <row r="260">
@@ -5100,13 +5106,13 @@
         <v>262</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>28.66</v>
+        <v>28.81</v>
       </c>
       <c r="C260" s="2" t="n">
-        <v>12336</v>
+        <v>21719</v>
       </c>
       <c r="D260" s="2" t="n">
-        <v>684438.5</v>
+        <v>727604</v>
       </c>
     </row>
     <row r="261">
@@ -5114,13 +5120,13 @@
         <v>263</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>28.59</v>
+        <v>28.76</v>
       </c>
       <c r="C261" s="2" t="n">
-        <v>6124</v>
+        <v>6855</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>843394.5</v>
+        <v>724150</v>
       </c>
     </row>
     <row r="262">
@@ -5128,13 +5134,13 @@
         <v>264</v>
       </c>
       <c r="B262" s="2" t="n">
-        <v>28.55</v>
+        <v>28.66</v>
       </c>
       <c r="C262" s="2" t="n">
-        <v>28516</v>
+        <v>12336</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>701570</v>
+        <v>684438.5</v>
       </c>
     </row>
     <row r="263">
@@ -5142,13 +5148,13 @@
         <v>265</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>28.54</v>
+        <v>28.59</v>
       </c>
       <c r="C263" s="2" t="n">
-        <v>77539</v>
+        <v>6124</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>760300</v>
+        <v>843394.5</v>
       </c>
     </row>
     <row r="264">
@@ -5156,13 +5162,13 @@
         <v>266</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>28.32</v>
+        <v>28.55</v>
       </c>
       <c r="C264" s="2" t="n">
-        <v>22845</v>
+        <v>28516</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>675824.5</v>
+        <v>701570</v>
       </c>
     </row>
     <row r="265">
@@ -5170,13 +5176,13 @@
         <v>267</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>28.27</v>
+        <v>28.54</v>
       </c>
       <c r="C265" s="2" t="n">
-        <v>10882</v>
+        <v>77539</v>
       </c>
       <c r="D265" s="2" t="n">
-        <v>837500</v>
+        <v>760300</v>
       </c>
     </row>
     <row r="266">
@@ -5184,13 +5190,13 @@
         <v>268</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>28.26</v>
+        <v>28.32</v>
       </c>
       <c r="C266" s="2" t="n">
-        <v>4954</v>
+        <v>22845</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>927618</v>
+        <v>675824.5</v>
       </c>
     </row>
     <row r="267">
@@ -5198,13 +5204,13 @@
         <v>269</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>28.22</v>
+        <v>28.27</v>
       </c>
       <c r="C267" s="2" t="n">
-        <v>10063</v>
+        <v>10882</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>768021</v>
+        <v>837500</v>
       </c>
     </row>
     <row r="268">
@@ -5212,13 +5218,13 @@
         <v>270</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>28.13</v>
+        <v>28.26</v>
       </c>
       <c r="C268" s="2" t="n">
-        <v>7980</v>
+        <v>4954</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>686827</v>
+        <v>927618</v>
       </c>
     </row>
     <row r="269">
@@ -5226,13 +5232,13 @@
         <v>271</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>28.1</v>
+        <v>28.22</v>
       </c>
       <c r="C269" s="2" t="n">
-        <v>5268</v>
+        <v>10063</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>866288</v>
+        <v>768021</v>
       </c>
     </row>
     <row r="270">
@@ -5240,13 +5246,13 @@
         <v>272</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>27.96</v>
+        <v>28.13</v>
       </c>
       <c r="C270" s="2" t="n">
-        <v>5489</v>
+        <v>7980</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>825238.5</v>
+        <v>686827</v>
       </c>
     </row>
     <row r="271">
@@ -5254,13 +5260,13 @@
         <v>273</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>27.95</v>
+        <v>28.1</v>
       </c>
       <c r="C271" s="2" t="n">
-        <v>47657</v>
+        <v>5268</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>707540</v>
+        <v>866288</v>
       </c>
     </row>
     <row r="272">
@@ -5268,13 +5274,13 @@
         <v>274</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>27.87</v>
+        <v>27.96</v>
       </c>
       <c r="C272" s="2" t="n">
-        <v>27659</v>
+        <v>5489</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>736132.5</v>
+        <v>825238.5</v>
       </c>
     </row>
     <row r="273">
@@ -5282,13 +5288,13 @@
         <v>275</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>27.86</v>
+        <v>27.95</v>
       </c>
       <c r="C273" s="2" t="n">
-        <v>7805</v>
+        <v>47657</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>648438</v>
+        <v>707540</v>
       </c>
     </row>
     <row r="274">
@@ -5296,13 +5302,13 @@
         <v>276</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>27.76</v>
+        <v>27.87</v>
       </c>
       <c r="C274" s="2" t="n">
-        <v>18408</v>
+        <v>27659</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>686129</v>
+        <v>736132.5</v>
       </c>
     </row>
     <row r="275">
@@ -5310,13 +5316,13 @@
         <v>277</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>27.74</v>
+        <v>27.86</v>
       </c>
       <c r="C275" s="2" t="n">
-        <v>7396</v>
+        <v>7805</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>625000</v>
+        <v>648438</v>
       </c>
     </row>
     <row r="276">
@@ -5324,13 +5330,13 @@
         <v>278</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>27.72</v>
+        <v>27.76</v>
       </c>
       <c r="C276" s="2" t="n">
-        <v>9129</v>
+        <v>18408</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>575000</v>
+        <v>686129</v>
       </c>
     </row>
     <row r="277">
@@ -5338,13 +5344,13 @@
         <v>279</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>27.71</v>
+        <v>27.74</v>
       </c>
       <c r="C277" s="2" t="n">
-        <v>1327</v>
+        <v>7396</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>796520</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="278">
@@ -5352,13 +5358,13 @@
         <v>280</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>27.52</v>
+        <v>27.72</v>
       </c>
       <c r="C278" s="2" t="n">
-        <v>15085</v>
+        <v>9129</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>642791</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="279">
@@ -5366,13 +5372,13 @@
         <v>281</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>27.49</v>
+        <v>27.71</v>
       </c>
       <c r="C279" s="2" t="n">
-        <v>21115</v>
+        <v>1327</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>679435</v>
+        <v>796520</v>
       </c>
     </row>
     <row r="280">
@@ -5380,13 +5386,13 @@
         <v>282</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>27.43</v>
+        <v>27.52</v>
       </c>
       <c r="C280" s="2" t="n">
-        <v>4668</v>
+        <v>15085</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>726455</v>
+        <v>642791</v>
       </c>
     </row>
     <row r="281">
@@ -5394,13 +5400,13 @@
         <v>283</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>27.32</v>
+        <v>27.49</v>
       </c>
       <c r="C281" s="2" t="n">
-        <v>37770</v>
+        <v>21115</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>720528</v>
+        <v>679435</v>
       </c>
     </row>
     <row r="282">
@@ -5408,13 +5414,13 @@
         <v>284</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>27.29</v>
+        <v>27.43</v>
       </c>
       <c r="C282" s="2" t="n">
-        <v>7168</v>
+        <v>4668</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>687500</v>
+        <v>726455</v>
       </c>
     </row>
     <row r="283">
@@ -5422,13 +5428,13 @@
         <v>285</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>27.28</v>
+        <v>27.32</v>
       </c>
       <c r="C283" s="2" t="n">
-        <v>5925</v>
+        <v>37770</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>918490</v>
+        <v>720528</v>
       </c>
     </row>
     <row r="284">
@@ -5436,13 +5442,13 @@
         <v>286</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>27.15</v>
+        <v>27.29</v>
       </c>
       <c r="C284" s="2" t="n">
-        <v>1522</v>
+        <v>7168</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>840454</v>
+        <v>687500</v>
       </c>
     </row>
     <row r="285">
@@ -5450,13 +5456,13 @@
         <v>287</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>27.09</v>
+        <v>27.28</v>
       </c>
       <c r="C285" s="2" t="n">
-        <v>4820</v>
+        <v>5925</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>962542</v>
+        <v>918490</v>
       </c>
     </row>
     <row r="286">
@@ -5464,13 +5470,13 @@
         <v>288</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>27.08</v>
+        <v>27.15</v>
       </c>
       <c r="C286" s="2" t="n">
-        <v>9910</v>
+        <v>1522</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>704458</v>
+        <v>840454</v>
       </c>
     </row>
     <row r="287">
@@ -5478,13 +5484,13 @@
         <v>289</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>26.98</v>
+        <v>27.09</v>
       </c>
       <c r="C287" s="2" t="n">
-        <v>5098</v>
+        <v>4820</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>795475</v>
+        <v>962542</v>
       </c>
     </row>
     <row r="288">
@@ -5492,13 +5498,13 @@
         <v>290</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>26.85</v>
+        <v>27.08</v>
       </c>
       <c r="C288" s="2" t="n">
-        <v>24240</v>
+        <v>9910</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>703906</v>
+        <v>704458</v>
       </c>
     </row>
     <row r="289">
@@ -5506,13 +5512,13 @@
         <v>291</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>26.83</v>
+        <v>26.98</v>
       </c>
       <c r="C289" s="2" t="n">
-        <v>24719</v>
+        <v>5098</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>763430</v>
+        <v>795475</v>
       </c>
     </row>
     <row r="290">
@@ -5520,13 +5526,13 @@
         <v>292</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>26.81</v>
+        <v>26.85</v>
       </c>
       <c r="C290" s="2" t="n">
-        <v>11786</v>
+        <v>24240</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>801406</v>
+        <v>703906</v>
       </c>
     </row>
     <row r="291">
@@ -5534,13 +5540,13 @@
         <v>293</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>26.71</v>
+        <v>26.83</v>
       </c>
       <c r="C291" s="2" t="n">
-        <v>3808</v>
+        <v>24719</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>625000</v>
+        <v>763430</v>
       </c>
     </row>
     <row r="292">
@@ -5548,13 +5554,13 @@
         <v>294</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>26.63</v>
+        <v>26.81</v>
       </c>
       <c r="C292" s="2" t="n">
-        <v>42825</v>
+        <v>11786</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>706188</v>
+        <v>801406</v>
       </c>
     </row>
     <row r="293">
@@ -5562,13 +5568,13 @@
         <v>295</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>26.54</v>
+        <v>26.71</v>
       </c>
       <c r="C293" s="2" t="n">
-        <v>7679</v>
+        <v>3808</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>758797</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="294">
@@ -5576,13 +5582,13 @@
         <v>296</v>
       </c>
       <c r="B294" s="2" t="n">
-        <v>26.49</v>
+        <v>26.63</v>
       </c>
       <c r="C294" s="2" t="n">
-        <v>898</v>
+        <v>42825</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>936570</v>
+        <v>706188</v>
       </c>
     </row>
     <row r="295">
@@ -5590,13 +5596,13 @@
         <v>297</v>
       </c>
       <c r="B295" s="2" t="n">
-        <v>26.36</v>
+        <v>26.54</v>
       </c>
       <c r="C295" s="2" t="n">
-        <v>26646</v>
+        <v>7679</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>840000</v>
+        <v>758797</v>
       </c>
     </row>
     <row r="296">
@@ -5604,13 +5610,13 @@
         <v>298</v>
       </c>
       <c r="B296" s="2" t="n">
-        <v>26.34</v>
+        <v>26.49</v>
       </c>
       <c r="C296" s="2" t="n">
-        <v>4809</v>
+        <v>898</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>778959.5</v>
+        <v>936570</v>
       </c>
     </row>
     <row r="297">
@@ -5618,13 +5624,13 @@
         <v>299</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>26.34</v>
+        <v>26.36</v>
       </c>
       <c r="C297" s="2" t="n">
-        <v>5470</v>
+        <v>26646</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>812386</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="298">
@@ -5632,13 +5638,13 @@
         <v>300</v>
       </c>
       <c r="B298" s="2" t="n">
-        <v>26.21</v>
+        <v>26.34</v>
       </c>
       <c r="C298" s="2" t="n">
-        <v>14083</v>
+        <v>4809</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>693162.5</v>
+        <v>778959.5</v>
       </c>
     </row>
     <row r="299">
@@ -5646,13 +5652,13 @@
         <v>301</v>
       </c>
       <c r="B299" s="2" t="n">
-        <v>26.19</v>
+        <v>26.34</v>
       </c>
       <c r="C299" s="2" t="n">
-        <v>381</v>
+        <v>5470</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>695290.5</v>
+        <v>812386</v>
       </c>
     </row>
     <row r="300">
@@ -5660,13 +5666,13 @@
         <v>302</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>26.02</v>
+        <v>26.21</v>
       </c>
       <c r="C300" s="2" t="n">
-        <v>8484</v>
+        <v>14083</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>848509</v>
+        <v>693162.5</v>
       </c>
     </row>
     <row r="301">
@@ -5674,13 +5680,13 @@
         <v>303</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>25.94</v>
+        <v>26.19</v>
       </c>
       <c r="C301" s="2" t="n">
-        <v>15355</v>
+        <v>381</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>665057</v>
+        <v>695290.5</v>
       </c>
     </row>
     <row r="302">
@@ -5688,13 +5694,13 @@
         <v>304</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>25.94</v>
+        <v>26.02</v>
       </c>
       <c r="C302" s="2" t="n">
-        <v>1427</v>
+        <v>8484</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>977960</v>
+        <v>848509</v>
       </c>
     </row>
     <row r="303">
@@ -5702,13 +5708,13 @@
         <v>305</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>25.9</v>
+        <v>25.94</v>
       </c>
       <c r="C303" s="2" t="n">
-        <v>37082</v>
+        <v>15355</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>722010</v>
+        <v>665057</v>
       </c>
     </row>
     <row r="304">
@@ -5716,13 +5722,13 @@
         <v>306</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>25.84</v>
+        <v>25.94</v>
       </c>
       <c r="C304" s="2" t="n">
-        <v>3618</v>
+        <v>1427</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>895375</v>
+        <v>977960</v>
       </c>
     </row>
     <row r="305">
@@ -5730,13 +5736,13 @@
         <v>307</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>25.79</v>
+        <v>25.9</v>
       </c>
       <c r="C305" s="2" t="n">
-        <v>13691</v>
+        <v>37082</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>725200</v>
+        <v>722010</v>
       </c>
     </row>
     <row r="306">
@@ -5744,13 +5750,13 @@
         <v>308</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>25.76</v>
+        <v>25.84</v>
       </c>
       <c r="C306" s="2" t="n">
-        <v>9749</v>
+        <v>3618</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>673611</v>
+        <v>895375</v>
       </c>
     </row>
     <row r="307">
@@ -5758,13 +5764,13 @@
         <v>309</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>25.57</v>
+        <v>25.79</v>
       </c>
       <c r="C307" s="2" t="n">
-        <v>21768</v>
+        <v>13691</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>846800</v>
+        <v>725200</v>
       </c>
     </row>
     <row r="308">
@@ -5772,13 +5778,13 @@
         <v>310</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>25.53</v>
+        <v>25.76</v>
       </c>
       <c r="C308" s="2" t="n">
-        <v>11704</v>
+        <v>9749</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>625000</v>
+        <v>673611</v>
       </c>
     </row>
     <row r="309">
@@ -5786,13 +5792,13 @@
         <v>311</v>
       </c>
       <c r="B309" s="2" t="n">
-        <v>25.3</v>
+        <v>25.57</v>
       </c>
       <c r="C309" s="2" t="n">
-        <v>16739</v>
+        <v>21768</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>831210</v>
+        <v>846800</v>
       </c>
     </row>
     <row r="310">
@@ -5800,13 +5806,13 @@
         <v>312</v>
       </c>
       <c r="B310" s="2" t="n">
-        <v>25.18</v>
+        <v>25.53</v>
       </c>
       <c r="C310" s="2" t="n">
-        <v>27156</v>
+        <v>11704</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>691100</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="311">
@@ -5814,13 +5820,13 @@
         <v>313</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>25.16</v>
+        <v>25.3</v>
       </c>
       <c r="C311" s="2" t="n">
-        <v>5878</v>
+        <v>16739</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>634944</v>
+        <v>831210</v>
       </c>
     </row>
     <row r="312">
@@ -5828,13 +5834,13 @@
         <v>314</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>25</v>
+        <v>25.18</v>
       </c>
       <c r="C312" s="2" t="n">
-        <v>4885</v>
+        <v>27156</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>757377</v>
+        <v>691100</v>
       </c>
     </row>
     <row r="313">
@@ -5842,13 +5848,13 @@
         <v>315</v>
       </c>
       <c r="B313" s="2" t="n">
-        <v>24.92</v>
+        <v>25.16</v>
       </c>
       <c r="C313" s="2" t="n">
-        <v>3492</v>
+        <v>5878</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>876500</v>
+        <v>634944</v>
       </c>
     </row>
     <row r="314">
@@ -5856,13 +5862,13 @@
         <v>316</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>24.68</v>
+        <v>25</v>
       </c>
       <c r="C314" s="2" t="n">
-        <v>28041</v>
+        <v>4885</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>737562</v>
+        <v>757377</v>
       </c>
     </row>
     <row r="315">
@@ -5870,13 +5876,13 @@
         <v>317</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>24.61</v>
+        <v>24.92</v>
       </c>
       <c r="C315" s="2" t="n">
-        <v>14647</v>
+        <v>3492</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>710610</v>
+        <v>876500</v>
       </c>
     </row>
     <row r="316">
@@ -5884,13 +5890,13 @@
         <v>318</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>24.5</v>
+        <v>24.68</v>
       </c>
       <c r="C316" s="2" t="n">
-        <v>14123</v>
+        <v>28041</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>652765</v>
+        <v>737562</v>
       </c>
     </row>
     <row r="317">
@@ -5898,13 +5904,13 @@
         <v>319</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>24.49</v>
+        <v>24.61</v>
       </c>
       <c r="C317" s="2" t="n">
-        <v>10742</v>
+        <v>14647</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>708568</v>
+        <v>710610</v>
       </c>
     </row>
     <row r="318">
@@ -5912,13 +5918,13 @@
         <v>320</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>24.47</v>
+        <v>24.5</v>
       </c>
       <c r="C318" s="2" t="n">
-        <v>12673</v>
+        <v>14123</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>735745</v>
+        <v>652765</v>
       </c>
     </row>
     <row r="319">
@@ -5926,13 +5932,13 @@
         <v>321</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>24.45</v>
+        <v>24.49</v>
       </c>
       <c r="C319" s="2" t="n">
-        <v>14656</v>
+        <v>10742</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>650164</v>
+        <v>708568</v>
       </c>
     </row>
     <row r="320">
@@ -5940,13 +5946,13 @@
         <v>322</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>24.33</v>
+        <v>24.47</v>
       </c>
       <c r="C320" s="2" t="n">
-        <v>19319</v>
+        <v>12673</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>736100</v>
+        <v>735745</v>
       </c>
     </row>
     <row r="321">
@@ -5954,13 +5960,13 @@
         <v>323</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>24.08</v>
+        <v>24.45</v>
       </c>
       <c r="C321" s="2" t="n">
-        <v>17406</v>
+        <v>14656</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>642084</v>
+        <v>650164</v>
       </c>
     </row>
     <row r="322">
@@ -5968,13 +5974,13 @@
         <v>324</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>24.03</v>
+        <v>24.33</v>
       </c>
       <c r="C322" s="2" t="n">
-        <v>20971</v>
+        <v>19319</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>730100</v>
+        <v>736100</v>
       </c>
     </row>
     <row r="323">
@@ -5982,13 +5988,13 @@
         <v>325</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>24.02</v>
+        <v>24.08</v>
       </c>
       <c r="C323" s="2" t="n">
-        <v>22034</v>
+        <v>17406</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>747810</v>
+        <v>642084</v>
       </c>
     </row>
     <row r="324">
@@ -5996,13 +6002,13 @@
         <v>326</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>23.95</v>
+        <v>24.03</v>
       </c>
       <c r="C324" s="2" t="n">
-        <v>3038</v>
+        <v>20971</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>904680</v>
+        <v>730100</v>
       </c>
     </row>
     <row r="325">
@@ -6010,13 +6016,13 @@
         <v>327</v>
       </c>
       <c r="B325" s="2" t="n">
-        <v>23.9</v>
+        <v>24.02</v>
       </c>
       <c r="C325" s="2" t="n">
-        <v>5937</v>
+        <v>22034</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>634902</v>
+        <v>747810</v>
       </c>
     </row>
     <row r="326">
@@ -6024,13 +6030,13 @@
         <v>328</v>
       </c>
       <c r="B326" s="2" t="n">
-        <v>23.88</v>
+        <v>23.95</v>
       </c>
       <c r="C326" s="2" t="n">
-        <v>20911</v>
+        <v>3038</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>663060</v>
+        <v>904680</v>
       </c>
     </row>
     <row r="327">
@@ -6038,13 +6044,13 @@
         <v>329</v>
       </c>
       <c r="B327" s="2" t="n">
-        <v>23.53</v>
+        <v>23.9</v>
       </c>
       <c r="C327" s="2" t="n">
-        <v>8602</v>
+        <v>5937</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>787393</v>
+        <v>634902</v>
       </c>
     </row>
     <row r="328">
@@ -6052,13 +6058,13 @@
         <v>330</v>
       </c>
       <c r="B328" s="2" t="n">
-        <v>23.46</v>
+        <v>23.88</v>
       </c>
       <c r="C328" s="2" t="n">
-        <v>11065</v>
+        <v>20911</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>685462</v>
+        <v>663060</v>
       </c>
     </row>
     <row r="329">
@@ -6066,13 +6072,13 @@
         <v>331</v>
       </c>
       <c r="B329" s="2" t="n">
-        <v>23.28</v>
+        <v>23.53</v>
       </c>
       <c r="C329" s="2" t="n">
-        <v>7479</v>
+        <v>8602</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>625000</v>
+        <v>787393</v>
       </c>
     </row>
     <row r="330">
@@ -6080,13 +6086,13 @@
         <v>332</v>
       </c>
       <c r="B330" s="2" t="n">
-        <v>23.21</v>
+        <v>23.46</v>
       </c>
       <c r="C330" s="2" t="n">
-        <v>12432</v>
+        <v>11065</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>672043</v>
+        <v>685462</v>
       </c>
     </row>
     <row r="331">
@@ -6094,13 +6100,13 @@
         <v>333</v>
       </c>
       <c r="B331" s="2" t="n">
-        <v>23.19</v>
+        <v>23.28</v>
       </c>
       <c r="C331" s="2" t="n">
-        <v>4817</v>
+        <v>7479</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>670108</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="332">
@@ -6108,13 +6114,13 @@
         <v>334</v>
       </c>
       <c r="B332" s="2" t="n">
-        <v>23</v>
+        <v>23.21</v>
       </c>
       <c r="C332" s="2" t="n">
-        <v>8515</v>
+        <v>12432</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>763910</v>
+        <v>672043</v>
       </c>
     </row>
     <row r="333">
@@ -6122,13 +6128,13 @@
         <v>335</v>
       </c>
       <c r="B333" s="2" t="n">
-        <v>22.76</v>
+        <v>23.19</v>
       </c>
       <c r="C333" s="2" t="n">
-        <v>22855</v>
+        <v>4817</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>737577</v>
+        <v>670108</v>
       </c>
     </row>
     <row r="334">
@@ -6136,13 +6142,13 @@
         <v>336</v>
       </c>
       <c r="B334" s="2" t="n">
-        <v>22.48</v>
+        <v>23</v>
       </c>
       <c r="C334" s="2" t="n">
-        <v>27227</v>
+        <v>8515</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>711296</v>
+        <v>763910</v>
       </c>
     </row>
     <row r="335">
@@ -6150,13 +6156,13 @@
         <v>337</v>
       </c>
       <c r="B335" s="2" t="n">
-        <v>22.4</v>
+        <v>22.76</v>
       </c>
       <c r="C335" s="2" t="n">
-        <v>9575</v>
+        <v>22855</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>701105</v>
+        <v>737577</v>
       </c>
     </row>
     <row r="336">
@@ -6164,13 +6170,13 @@
         <v>338</v>
       </c>
       <c r="B336" s="2" t="n">
-        <v>22.31</v>
+        <v>22.48</v>
       </c>
       <c r="C336" s="2" t="n">
-        <v>585</v>
+        <v>27227</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>640000</v>
+        <v>711296</v>
       </c>
     </row>
     <row r="337">
@@ -6178,13 +6184,13 @@
         <v>339</v>
       </c>
       <c r="B337" s="2" t="n">
-        <v>22.24</v>
+        <v>22.4</v>
       </c>
       <c r="C337" s="2" t="n">
-        <v>5686</v>
+        <v>9575</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>657329</v>
+        <v>701105</v>
       </c>
     </row>
     <row r="338">
@@ -6192,13 +6198,13 @@
         <v>340</v>
       </c>
       <c r="B338" s="2" t="n">
-        <v>21.89</v>
+        <v>22.31</v>
       </c>
       <c r="C338" s="2" t="n">
-        <v>9476</v>
+        <v>585</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>655613</v>
+        <v>640000</v>
       </c>
     </row>
     <row r="339">
@@ -6206,13 +6212,13 @@
         <v>341</v>
       </c>
       <c r="B339" s="2" t="n">
-        <v>21.58</v>
+        <v>22.24</v>
       </c>
       <c r="C339" s="2" t="n">
-        <v>21688</v>
+        <v>5686</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>813510</v>
+        <v>657329</v>
       </c>
     </row>
     <row r="340">
@@ -6220,13 +6226,13 @@
         <v>342</v>
       </c>
       <c r="B340" s="2" t="n">
-        <v>21.56</v>
+        <v>21.89</v>
       </c>
       <c r="C340" s="2" t="n">
-        <v>11090</v>
+        <v>9476</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>792662</v>
+        <v>655613</v>
       </c>
     </row>
     <row r="341">
@@ -6234,13 +6240,13 @@
         <v>343</v>
       </c>
       <c r="B341" s="2" t="n">
-        <v>20.81</v>
+        <v>21.58</v>
       </c>
       <c r="C341" s="2" t="n">
-        <v>1335</v>
+        <v>21688</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>845239.5</v>
+        <v>813510</v>
       </c>
     </row>
     <row r="342">
@@ -6248,13 +6254,13 @@
         <v>344</v>
       </c>
       <c r="B342" s="2" t="n">
-        <v>20.39</v>
+        <v>21.56</v>
       </c>
       <c r="C342" s="2" t="n">
-        <v>17839</v>
+        <v>11090</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>666274</v>
+        <v>792662</v>
       </c>
     </row>
     <row r="343">
@@ -6262,13 +6268,13 @@
         <v>345</v>
       </c>
       <c r="B343" s="2" t="n">
-        <v>19.62</v>
+        <v>20.81</v>
       </c>
       <c r="C343" s="2" t="n">
-        <v>14330</v>
+        <v>1335</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>625000</v>
+        <v>845239.5</v>
       </c>
     </row>
     <row r="344">
@@ -6276,13 +6282,13 @@
         <v>346</v>
       </c>
       <c r="B344" s="2" t="n">
-        <v>19.59</v>
+        <v>20.39</v>
       </c>
       <c r="C344" s="2" t="n">
-        <v>4526</v>
+        <v>17839</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>885213</v>
+        <v>666274</v>
       </c>
     </row>
     <row r="345">
@@ -6290,17 +6296,45 @@
         <v>347</v>
       </c>
       <c r="B345" s="2" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="C345" s="2" t="n">
+        <v>14330</v>
+      </c>
+      <c r="D345" s="2" t="n">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B346" s="2" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>4526</v>
+      </c>
+      <c r="D346" s="2" t="n">
+        <v>885213</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B347" s="2" t="n">
         <v>17.33</v>
       </c>
-      <c r="C345" s="2" t="n">
+      <c r="C347" s="2" t="n">
         <v>8608</v>
       </c>
-      <c r="D345" s="2" t="n">
+      <c r="D347" s="2" t="n">
         <v>690001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D345"/>
+  <autoFilter ref="A1:D347"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -6317,7 +6351,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6325,50 +6359,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
